--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:43</t>
+    <t xml:space="preserve">2026-09-09 23:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:42</t>
+    <t xml:space="preserve">2026-09-18 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:31</t>
+    <t xml:space="preserve">2026-09-23 13:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:03</t>
+    <t xml:space="preserve">2026-10-02 15:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:33</t>
+    <t xml:space="preserve">2026-10-05 13:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
